--- a/data/실버보험 신계약가이드라인.xlsx
+++ b/data/실버보험 신계약가이드라인.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suhyang\Desktop\uwagent\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F511E564-1C90-4EF0-B2AB-0F3A563231EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C7E688-49BF-42FF-859F-691CD64876BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F3C78F31-5B33-42D9-9C51-67EDE9CD2D7A}"/>
   </bookViews>
@@ -93,10 +93,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>주2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>파워수술</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -216,6 +212,10 @@
   </si>
   <si>
     <t xml:space="preserve">ㅇ 상품코드 : LP030405 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -336,11 +336,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,17 +686,17 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.4">
@@ -779,11 +779,11 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B10" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>12</v>
@@ -802,14 +802,14 @@
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B11" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="F11" s="2">
         <v>1000</v>
@@ -824,12 +824,12 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="7" t="s">
-        <v>14</v>
+      <c r="B12" s="8" t="s">
+        <v>13</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="2"/>
@@ -841,13 +841,13 @@
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B13" s="4"/>
       <c r="C13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="E13" s="7" t="s">
         <v>17</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="F13" s="2">
         <v>100</v>
@@ -870,10 +870,10 @@
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B14" s="4"/>
       <c r="C14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="2">
@@ -897,10 +897,10 @@
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B15" s="4"/>
       <c r="C15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>22</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="2">
@@ -924,10 +924,10 @@
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B16" s="4"/>
       <c r="C16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="2">
@@ -951,10 +951,10 @@
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B17" s="5"/>
       <c r="C17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="2">
@@ -977,14 +977,14 @@
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B18" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="F18" s="2">
         <v>3000</v>
@@ -1000,14 +1000,14 @@
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B19" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C19" s="6"/>
       <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="F19" s="2">
         <v>5000</v>
@@ -1023,41 +1023,36 @@
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B25" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="F6:I6"/>
-    <mergeCell ref="J6:J8"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="E13:E17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="B6:C8"/>
     <mergeCell ref="D6:D8"/>
@@ -1067,6 +1062,11 @@
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="F6:I6"/>
+    <mergeCell ref="J6:J8"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="E13:E17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
